--- a/data/LesJO.xlsx
+++ b/data/LesJO.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LesSportifsEQ" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,10 @@
     <sheet name="LesInscriptions" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="LesResultats" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">LesInscriptions!$A$1:$B$422</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">LesSportifsEQ!$A$1:$G$349</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -2749,7 +2753,24 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10682,10 +10703,11 @@
         <v>810</v>
       </c>
       <c r="G349" s="1" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G349"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10693,6 +10715,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11594,10 +11617,10 @@
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>814</v>
       </c>
     </row>
@@ -14966,6 +14989,7 @@
       <c r="B422" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B422"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -14973,6 +14997,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15076,7 +15101,7 @@
         <v>1276</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>1087</v>
